--- a/f2_tabelas/tabela_obitos_por_ano_e_rras.xlsx
+++ b/f2_tabelas/tabela_obitos_por_ano_e_rras.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C241"/>
+  <dimension ref="A1:C248"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -377,7 +377,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RRAS1</t>
+          <t>RRAS 1</t>
         </is>
       </c>
       <c r="C2">
@@ -390,11 +390,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RRAS10</t>
+          <t>RRAS 2</t>
         </is>
       </c>
       <c r="C3">
-        <v>99</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4">
@@ -403,11 +403,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RRAS11</t>
+          <t>RRAS 3</t>
         </is>
       </c>
       <c r="C4">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -416,11 +416,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RRAS12</t>
+          <t>RRAS 4</t>
         </is>
       </c>
       <c r="C5">
-        <v>134</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6">
@@ -429,11 +429,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RRAS13</t>
+          <t>RRAS 5</t>
         </is>
       </c>
       <c r="C6">
-        <v>260</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7">
@@ -442,11 +442,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RRAS14</t>
+          <t>RRAS 6</t>
         </is>
       </c>
       <c r="C7">
-        <v>156</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="8">
@@ -455,11 +455,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RRAS15</t>
+          <t>RRAS 7</t>
         </is>
       </c>
       <c r="C8">
-        <v>360</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -468,11 +468,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RRAS16</t>
+          <t>RRAS 8</t>
         </is>
       </c>
       <c r="C9">
-        <v>111</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -481,11 +481,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RRAS17</t>
+          <t>RRAS 9</t>
         </is>
       </c>
       <c r="C10">
-        <v>234</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11">
@@ -494,11 +494,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RRAS18</t>
+          <t>RRAS 10</t>
         </is>
       </c>
       <c r="C11">
-        <v>83</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -507,11 +507,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RRAS19</t>
+          <t>RRAS 11</t>
         </is>
       </c>
       <c r="C12">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -520,11 +520,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RRAS2</t>
+          <t>RRAS 12</t>
         </is>
       </c>
       <c r="C13">
-        <v>391</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14">
@@ -533,11 +533,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RRAS3</t>
+          <t>RRAS 13</t>
         </is>
       </c>
       <c r="C14">
-        <v>80</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15">
@@ -546,11 +546,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RRAS4</t>
+          <t>RRAS 14</t>
         </is>
       </c>
       <c r="C15">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16">
@@ -559,11 +559,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RRAS5</t>
+          <t>RRAS 15</t>
         </is>
       </c>
       <c r="C16">
-        <v>239</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17">
@@ -572,11 +572,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RRAS6</t>
+          <t>RRAS 16</t>
         </is>
       </c>
       <c r="C17">
-        <v>1159</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
@@ -585,11 +585,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RRAS7</t>
+          <t>RRAS 17</t>
         </is>
       </c>
       <c r="C18">
-        <v>293</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19">
@@ -598,32 +598,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RRAS8</t>
+          <t>RRAS 18</t>
         </is>
       </c>
       <c r="C19">
-        <v>269</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
         <v>2012</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>RRAS9</t>
-        </is>
-      </c>
       <c r="C20">
-        <v>196</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>2012</v>
+        <v>2013</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RRAS 1</t>
+        </is>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22">
@@ -632,11 +632,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RRAS1</t>
+          <t>RRAS 2</t>
         </is>
       </c>
       <c r="C22">
-        <v>243</v>
+        <v>366</v>
       </c>
     </row>
     <row r="23">
@@ -645,11 +645,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RRAS10</t>
+          <t>RRAS 3</t>
         </is>
       </c>
       <c r="C23">
-        <v>99</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
@@ -658,11 +658,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RRAS11</t>
+          <t>RRAS 4</t>
         </is>
       </c>
       <c r="C24">
-        <v>62</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25">
@@ -671,11 +671,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RRAS12</t>
+          <t>RRAS 5</t>
         </is>
       </c>
       <c r="C25">
-        <v>115</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26">
@@ -684,11 +684,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RRAS13</t>
+          <t>RRAS 6</t>
         </is>
       </c>
       <c r="C26">
-        <v>261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="27">
@@ -697,11 +697,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RRAS14</t>
+          <t>RRAS 7</t>
         </is>
       </c>
       <c r="C27">
-        <v>156</v>
+        <v>274</v>
       </c>
     </row>
     <row r="28">
@@ -710,11 +710,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RRAS15</t>
+          <t>RRAS 8</t>
         </is>
       </c>
       <c r="C28">
-        <v>329</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29">
@@ -723,11 +723,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RRAS16</t>
+          <t>RRAS 9</t>
         </is>
       </c>
       <c r="C29">
-        <v>122</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30">
@@ -736,11 +736,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RRAS17</t>
+          <t>RRAS 10</t>
         </is>
       </c>
       <c r="C30">
-        <v>253</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31">
@@ -749,11 +749,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RRAS18</t>
+          <t>RRAS 11</t>
         </is>
       </c>
       <c r="C31">
-        <v>111</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32">
@@ -762,11 +762,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RRAS19</t>
+          <t>RRAS 12</t>
         </is>
       </c>
       <c r="C32">
-        <v>59</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33">
@@ -775,11 +775,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RRAS2</t>
+          <t>RRAS 13</t>
         </is>
       </c>
       <c r="C33">
-        <v>366</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34">
@@ -788,11 +788,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RRAS3</t>
+          <t>RRAS 14</t>
         </is>
       </c>
       <c r="C34">
-        <v>75</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35">
@@ -801,11 +801,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RRAS4</t>
+          <t>RRAS 15</t>
         </is>
       </c>
       <c r="C35">
-        <v>143</v>
+        <v>329</v>
       </c>
     </row>
     <row r="36">
@@ -814,11 +814,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RRAS5</t>
+          <t>RRAS 16</t>
         </is>
       </c>
       <c r="C36">
-        <v>216</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37">
@@ -827,11 +827,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RRAS6</t>
+          <t>RRAS 17</t>
         </is>
       </c>
       <c r="C37">
-        <v>1260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="38">
@@ -840,45 +840,45 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RRAS7</t>
+          <t>RRAS 18</t>
         </is>
       </c>
       <c r="C38">
-        <v>274</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
         <v>2013</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>RRAS8</t>
-        </is>
-      </c>
       <c r="C39">
-        <v>229</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RRAS9</t>
+          <t>RRAS 1</t>
         </is>
       </c>
       <c r="C40">
-        <v>159</v>
+        <v>253</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>2013</v>
+        <v>2014</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>RRAS 2</t>
+        </is>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>364</v>
       </c>
     </row>
     <row r="42">
@@ -887,11 +887,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RRAS1</t>
+          <t>RRAS 3</t>
         </is>
       </c>
       <c r="C42">
-        <v>253</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43">
@@ -900,11 +900,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RRAS10</t>
+          <t>RRAS 4</t>
         </is>
       </c>
       <c r="C43">
-        <v>126</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44">
@@ -913,11 +913,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RRAS11</t>
+          <t>RRAS 5</t>
         </is>
       </c>
       <c r="C44">
-        <v>58</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45">
@@ -926,11 +926,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RRAS12</t>
+          <t>RRAS 6</t>
         </is>
       </c>
       <c r="C45">
-        <v>106</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="46">
@@ -939,11 +939,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RRAS13</t>
+          <t>RRAS 7</t>
         </is>
       </c>
       <c r="C46">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="47">
@@ -952,11 +952,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RRAS14</t>
+          <t>RRAS 8</t>
         </is>
       </c>
       <c r="C47">
-        <v>132</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48">
@@ -965,11 +965,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RRAS15</t>
+          <t>RRAS 9</t>
         </is>
       </c>
       <c r="C48">
-        <v>396</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49">
@@ -978,11 +978,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RRAS16</t>
+          <t>RRAS 10</t>
         </is>
       </c>
       <c r="C49">
-        <v>115</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50">
@@ -991,11 +991,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RRAS17</t>
+          <t>RRAS 11</t>
         </is>
       </c>
       <c r="C50">
-        <v>254</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51">
@@ -1004,11 +1004,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RRAS18</t>
+          <t>RRAS 12</t>
         </is>
       </c>
       <c r="C51">
-        <v>87</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52">
@@ -1017,11 +1017,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RRAS19</t>
+          <t>RRAS 13</t>
         </is>
       </c>
       <c r="C52">
-        <v>58</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53">
@@ -1030,11 +1030,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RRAS2</t>
+          <t>RRAS 14</t>
         </is>
       </c>
       <c r="C53">
-        <v>364</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54">
@@ -1043,11 +1043,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RRAS3</t>
+          <t>RRAS 15</t>
         </is>
       </c>
       <c r="C54">
-        <v>97</v>
+        <v>396</v>
       </c>
     </row>
     <row r="55">
@@ -1056,11 +1056,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RRAS4</t>
+          <t>RRAS 16</t>
         </is>
       </c>
       <c r="C55">
-        <v>166</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RRAS5</t>
+          <t>RRAS 17</t>
         </is>
       </c>
       <c r="C56">
-        <v>182</v>
+        <v>254</v>
       </c>
     </row>
     <row r="57">
@@ -1082,58 +1082,58 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RRAS6</t>
+          <t>RRAS 18</t>
         </is>
       </c>
       <c r="C57">
-        <v>1271</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
         <v>2014</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>RRAS7</t>
-        </is>
-      </c>
       <c r="C58">
-        <v>282</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RRAS8</t>
+          <t>RRAS 1</t>
         </is>
       </c>
       <c r="C59">
-        <v>222</v>
+        <v>276</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RRAS9</t>
+          <t>RRAS 2</t>
         </is>
       </c>
       <c r="C60">
-        <v>172</v>
+        <v>371</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>2014</v>
+        <v>2015</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>RRAS 3</t>
+        </is>
       </c>
       <c r="C61">
-        <v>6</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62">
@@ -1142,11 +1142,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RRAS1</t>
+          <t>RRAS 4</t>
         </is>
       </c>
       <c r="C62">
-        <v>276</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63">
@@ -1155,11 +1155,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RRAS10</t>
+          <t>RRAS 5</t>
         </is>
       </c>
       <c r="C63">
-        <v>115</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64">
@@ -1168,11 +1168,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RRAS11</t>
+          <t>RRAS 6</t>
         </is>
       </c>
       <c r="C64">
-        <v>80</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="65">
@@ -1181,11 +1181,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RRAS12</t>
+          <t>RRAS 7</t>
         </is>
       </c>
       <c r="C65">
-        <v>126</v>
+        <v>294</v>
       </c>
     </row>
     <row r="66">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RRAS13</t>
+          <t>RRAS 8</t>
         </is>
       </c>
       <c r="C66">
-        <v>284</v>
+        <v>241</v>
       </c>
     </row>
     <row r="67">
@@ -1207,11 +1207,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RRAS14</t>
+          <t>RRAS 9</t>
         </is>
       </c>
       <c r="C67">
-        <v>147</v>
+        <v>167</v>
       </c>
     </row>
     <row r="68">
@@ -1220,11 +1220,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RRAS15</t>
+          <t>RRAS 10</t>
         </is>
       </c>
       <c r="C68">
-        <v>371</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RRAS16</t>
+          <t>RRAS 11</t>
         </is>
       </c>
       <c r="C69">
-        <v>137</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70">
@@ -1246,11 +1246,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RRAS17</t>
+          <t>RRAS 12</t>
         </is>
       </c>
       <c r="C70">
-        <v>268</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RRAS18</t>
+          <t>RRAS 13</t>
         </is>
       </c>
       <c r="C71">
-        <v>121</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RRAS19</t>
+          <t>RRAS 14</t>
         </is>
       </c>
       <c r="C72">
-        <v>66</v>
+        <v>147</v>
       </c>
     </row>
     <row r="73">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RRAS2</t>
+          <t>RRAS 15</t>
         </is>
       </c>
       <c r="C73">
@@ -1298,11 +1298,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RRAS3</t>
+          <t>RRAS 16</t>
         </is>
       </c>
       <c r="C74">
-        <v>87</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75">
@@ -1311,11 +1311,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RRAS4</t>
+          <t>RRAS 17</t>
         </is>
       </c>
       <c r="C75">
-        <v>159</v>
+        <v>268</v>
       </c>
     </row>
     <row r="76">
@@ -1324,71 +1324,71 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RRAS5</t>
+          <t>RRAS 18</t>
         </is>
       </c>
       <c r="C76">
-        <v>234</v>
+        <v>121</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
         <v>2015</v>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>RRAS6</t>
-        </is>
-      </c>
       <c r="C77">
-        <v>1282</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RRAS7</t>
+          <t>RRAS 1</t>
         </is>
       </c>
       <c r="C78">
-        <v>294</v>
+        <v>232</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RRAS8</t>
+          <t>RRAS 2</t>
         </is>
       </c>
       <c r="C79">
-        <v>241</v>
+        <v>357</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RRAS9</t>
+          <t>RRAS 3</t>
         </is>
       </c>
       <c r="C80">
-        <v>167</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>2015</v>
+        <v>2016</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>RRAS 4</t>
+        </is>
       </c>
       <c r="C81">
-        <v>4</v>
+        <v>144</v>
       </c>
     </row>
     <row r="82">
@@ -1397,11 +1397,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RRAS1</t>
+          <t>RRAS 5</t>
         </is>
       </c>
       <c r="C82">
-        <v>232</v>
+        <v>223</v>
       </c>
     </row>
     <row r="83">
@@ -1410,11 +1410,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RRAS10</t>
+          <t>RRAS 6</t>
         </is>
       </c>
       <c r="C83">
-        <v>105</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="84">
@@ -1423,11 +1423,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RRAS11</t>
+          <t>RRAS 7</t>
         </is>
       </c>
       <c r="C84">
-        <v>87</v>
+        <v>263</v>
       </c>
     </row>
     <row r="85">
@@ -1436,11 +1436,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RRAS12</t>
+          <t>RRAS 8</t>
         </is>
       </c>
       <c r="C85">
-        <v>119</v>
+        <v>238</v>
       </c>
     </row>
     <row r="86">
@@ -1449,11 +1449,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RRAS13</t>
+          <t>RRAS 9</t>
         </is>
       </c>
       <c r="C86">
-        <v>266</v>
+        <v>176</v>
       </c>
     </row>
     <row r="87">
@@ -1462,11 +1462,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RRAS14</t>
+          <t>RRAS 10</t>
         </is>
       </c>
       <c r="C87">
-        <v>152</v>
+        <v>105</v>
       </c>
     </row>
     <row r="88">
@@ -1475,11 +1475,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>RRAS15</t>
+          <t>RRAS 11</t>
         </is>
       </c>
       <c r="C88">
-        <v>368</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89">
@@ -1488,11 +1488,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>RRAS16</t>
+          <t>RRAS 12</t>
         </is>
       </c>
       <c r="C89">
-        <v>111</v>
+        <v>176</v>
       </c>
     </row>
     <row r="90">
@@ -1501,11 +1501,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>RRAS17</t>
+          <t>RRAS 13</t>
         </is>
       </c>
       <c r="C90">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="91">
@@ -1514,11 +1514,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RRAS18</t>
+          <t>RRAS 14</t>
         </is>
       </c>
       <c r="C91">
-        <v>68</v>
+        <v>152</v>
       </c>
     </row>
     <row r="92">
@@ -1527,11 +1527,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RRAS19</t>
+          <t>RRAS 15</t>
         </is>
       </c>
       <c r="C92">
-        <v>57</v>
+        <v>368</v>
       </c>
     </row>
     <row r="93">
@@ -1540,11 +1540,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RRAS2</t>
+          <t>RRAS 16</t>
         </is>
       </c>
       <c r="C93">
-        <v>357</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94">
@@ -1553,11 +1553,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RRAS3</t>
+          <t>RRAS 17</t>
         </is>
       </c>
       <c r="C94">
-        <v>83</v>
+        <v>271</v>
       </c>
     </row>
     <row r="95">
@@ -1566,84 +1566,84 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>RRAS4</t>
+          <t>RRAS 18</t>
         </is>
       </c>
       <c r="C95">
-        <v>144</v>
+        <v>68</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
         <v>2016</v>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>RRAS5</t>
-        </is>
-      </c>
       <c r="C96">
-        <v>223</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RRAS6</t>
+          <t>RRAS 1</t>
         </is>
       </c>
       <c r="C97">
-        <v>1273</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>RRAS7</t>
+          <t>RRAS 2</t>
         </is>
       </c>
       <c r="C98">
-        <v>263</v>
+        <v>420</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RRAS8</t>
+          <t>RRAS 3</t>
         </is>
       </c>
       <c r="C99">
-        <v>238</v>
+        <v>82</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RRAS9</t>
+          <t>RRAS 4</t>
         </is>
       </c>
       <c r="C100">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>2016</v>
+        <v>2017</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>RRAS 5</t>
+        </is>
       </c>
       <c r="C101">
-        <v>4</v>
+        <v>211</v>
       </c>
     </row>
     <row r="102">
@@ -1652,11 +1652,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>RRAS1</t>
+          <t>RRAS 6</t>
         </is>
       </c>
       <c r="C102">
-        <v>216</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="103">
@@ -1665,11 +1665,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RRAS10</t>
+          <t>RRAS 7</t>
         </is>
       </c>
       <c r="C103">
-        <v>98</v>
+        <v>261</v>
       </c>
     </row>
     <row r="104">
@@ -1678,11 +1678,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>RRAS11</t>
+          <t>RRAS 8</t>
         </is>
       </c>
       <c r="C104">
-        <v>47</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105">
@@ -1691,11 +1691,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RRAS12</t>
+          <t>RRAS 9</t>
         </is>
       </c>
       <c r="C105">
-        <v>110</v>
+        <v>191</v>
       </c>
     </row>
     <row r="106">
@@ -1704,11 +1704,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RRAS13</t>
+          <t>RRAS 10</t>
         </is>
       </c>
       <c r="C106">
-        <v>237</v>
+        <v>98</v>
       </c>
     </row>
     <row r="107">
@@ -1717,11 +1717,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RRAS14</t>
+          <t>RRAS 11</t>
         </is>
       </c>
       <c r="C107">
-        <v>161</v>
+        <v>47</v>
       </c>
     </row>
     <row r="108">
@@ -1730,11 +1730,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RRAS15</t>
+          <t>RRAS 12</t>
         </is>
       </c>
       <c r="C108">
-        <v>332</v>
+        <v>174</v>
       </c>
     </row>
     <row r="109">
@@ -1743,11 +1743,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RRAS16</t>
+          <t>RRAS 13</t>
         </is>
       </c>
       <c r="C109">
-        <v>120</v>
+        <v>237</v>
       </c>
     </row>
     <row r="110">
@@ -1756,11 +1756,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RRAS17</t>
+          <t>RRAS 14</t>
         </is>
       </c>
       <c r="C110">
-        <v>236</v>
+        <v>161</v>
       </c>
     </row>
     <row r="111">
@@ -1769,11 +1769,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>RRAS18</t>
+          <t>RRAS 15</t>
         </is>
       </c>
       <c r="C111">
-        <v>73</v>
+        <v>332</v>
       </c>
     </row>
     <row r="112">
@@ -1782,11 +1782,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RRAS19</t>
+          <t>RRAS 16</t>
         </is>
       </c>
       <c r="C112">
-        <v>64</v>
+        <v>120</v>
       </c>
     </row>
     <row r="113">
@@ -1795,11 +1795,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RRAS2</t>
+          <t>RRAS 17</t>
         </is>
       </c>
       <c r="C113">
-        <v>420</v>
+        <v>236</v>
       </c>
     </row>
     <row r="114">
@@ -1808,97 +1808,97 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RRAS3</t>
+          <t>RRAS 18</t>
         </is>
       </c>
       <c r="C114">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="115">
       <c r="A115">
         <v>2017</v>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>RRAS4</t>
-        </is>
-      </c>
       <c r="C115">
-        <v>159</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RRAS5</t>
+          <t>RRAS 1</t>
         </is>
       </c>
       <c r="C116">
-        <v>211</v>
+        <v>236</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>RRAS6</t>
+          <t>RRAS 2</t>
         </is>
       </c>
       <c r="C117">
-        <v>1209</v>
+        <v>403</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>RRAS7</t>
+          <t>RRAS 3</t>
         </is>
       </c>
       <c r="C118">
-        <v>261</v>
+        <v>98</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>RRAS8</t>
+          <t>RRAS 4</t>
         </is>
       </c>
       <c r="C119">
-        <v>265</v>
+        <v>131</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RRAS9</t>
+          <t>RRAS 5</t>
         </is>
       </c>
       <c r="C120">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="121">
       <c r="A121">
-        <v>2017</v>
+        <v>2018</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>RRAS 6</t>
+        </is>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="122">
@@ -1907,11 +1907,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RRAS1</t>
+          <t>RRAS 7</t>
         </is>
       </c>
       <c r="C122">
-        <v>236</v>
+        <v>222</v>
       </c>
     </row>
     <row r="123">
@@ -1920,11 +1920,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RRAS10</t>
+          <t>RRAS 8</t>
         </is>
       </c>
       <c r="C123">
-        <v>93</v>
+        <v>254</v>
       </c>
     </row>
     <row r="124">
@@ -1933,11 +1933,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>RRAS11</t>
+          <t>RRAS 9</t>
         </is>
       </c>
       <c r="C124">
-        <v>82</v>
+        <v>170</v>
       </c>
     </row>
     <row r="125">
@@ -1946,11 +1946,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>RRAS12</t>
+          <t>RRAS 10</t>
         </is>
       </c>
       <c r="C125">
-        <v>114</v>
+        <v>93</v>
       </c>
     </row>
     <row r="126">
@@ -1959,11 +1959,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>RRAS13</t>
+          <t>RRAS 11</t>
         </is>
       </c>
       <c r="C126">
-        <v>223</v>
+        <v>82</v>
       </c>
     </row>
     <row r="127">
@@ -1972,11 +1972,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>RRAS14</t>
+          <t>RRAS 12</t>
         </is>
       </c>
       <c r="C127">
-        <v>156</v>
+        <v>185</v>
       </c>
     </row>
     <row r="128">
@@ -1985,11 +1985,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>RRAS15</t>
+          <t>RRAS 13</t>
         </is>
       </c>
       <c r="C128">
-        <v>323</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129">
@@ -1998,11 +1998,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>RRAS16</t>
+          <t>RRAS 14</t>
         </is>
       </c>
       <c r="C129">
-        <v>137</v>
+        <v>156</v>
       </c>
     </row>
     <row r="130">
@@ -2011,11 +2011,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>RRAS17</t>
+          <t>RRAS 15</t>
         </is>
       </c>
       <c r="C130">
-        <v>242</v>
+        <v>323</v>
       </c>
     </row>
     <row r="131">
@@ -2024,11 +2024,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>RRAS18</t>
+          <t>RRAS 16</t>
         </is>
       </c>
       <c r="C131">
-        <v>78</v>
+        <v>137</v>
       </c>
     </row>
     <row r="132">
@@ -2037,11 +2037,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>RRAS19</t>
+          <t>RRAS 17</t>
         </is>
       </c>
       <c r="C132">
-        <v>71</v>
+        <v>242</v>
       </c>
     </row>
     <row r="133">
@@ -2050,110 +2050,110 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>RRAS2</t>
+          <t>RRAS 18</t>
         </is>
       </c>
       <c r="C133">
-        <v>403</v>
+        <v>78</v>
       </c>
     </row>
     <row r="134">
       <c r="A134">
         <v>2018</v>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>RRAS3</t>
-        </is>
-      </c>
       <c r="C134">
-        <v>98</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>RRAS4</t>
+          <t>RRAS 1</t>
         </is>
       </c>
       <c r="C135">
-        <v>131</v>
+        <v>241</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>RRAS5</t>
+          <t>RRAS 2</t>
         </is>
       </c>
       <c r="C136">
-        <v>206</v>
+        <v>360</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>RRAS6</t>
+          <t>RRAS 3</t>
         </is>
       </c>
       <c r="C137">
-        <v>1221</v>
+        <v>76</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>RRAS7</t>
+          <t>RRAS 4</t>
         </is>
       </c>
       <c r="C138">
-        <v>222</v>
+        <v>147</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>RRAS8</t>
+          <t>RRAS 5</t>
         </is>
       </c>
       <c r="C139">
-        <v>254</v>
+        <v>239</v>
       </c>
     </row>
     <row r="140">
       <c r="A140">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>RRAS9</t>
+          <t>RRAS 6</t>
         </is>
       </c>
       <c r="C140">
-        <v>170</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="141">
       <c r="A141">
-        <v>2018</v>
+        <v>2019</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>RRAS 7</t>
+        </is>
       </c>
       <c r="C141">
-        <v>2</v>
+        <v>228</v>
       </c>
     </row>
     <row r="142">
@@ -2162,11 +2162,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>RRAS1</t>
+          <t>RRAS 8</t>
         </is>
       </c>
       <c r="C142">
-        <v>241</v>
+        <v>219</v>
       </c>
     </row>
     <row r="143">
@@ -2175,11 +2175,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>RRAS10</t>
+          <t>RRAS 9</t>
         </is>
       </c>
       <c r="C143">
-        <v>90</v>
+        <v>139</v>
       </c>
     </row>
     <row r="144">
@@ -2188,11 +2188,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>RRAS11</t>
+          <t>RRAS 10</t>
         </is>
       </c>
       <c r="C144">
-        <v>77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="145">
@@ -2201,11 +2201,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>RRAS12</t>
+          <t>RRAS 11</t>
         </is>
       </c>
       <c r="C145">
-        <v>127</v>
+        <v>77</v>
       </c>
     </row>
     <row r="146">
@@ -2214,11 +2214,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>RRAS13</t>
+          <t>RRAS 12</t>
         </is>
       </c>
       <c r="C146">
-        <v>225</v>
+        <v>196</v>
       </c>
     </row>
     <row r="147">
@@ -2227,11 +2227,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>RRAS14</t>
+          <t>RRAS 13</t>
         </is>
       </c>
       <c r="C147">
-        <v>139</v>
+        <v>225</v>
       </c>
     </row>
     <row r="148">
@@ -2240,11 +2240,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>RRAS15</t>
+          <t>RRAS 14</t>
         </is>
       </c>
       <c r="C148">
-        <v>318</v>
+        <v>139</v>
       </c>
     </row>
     <row r="149">
@@ -2253,11 +2253,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>RRAS16</t>
+          <t>RRAS 15</t>
         </is>
       </c>
       <c r="C149">
-        <v>124</v>
+        <v>318</v>
       </c>
     </row>
     <row r="150">
@@ -2266,11 +2266,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>RRAS17</t>
+          <t>RRAS 16</t>
         </is>
       </c>
       <c r="C150">
-        <v>226</v>
+        <v>124</v>
       </c>
     </row>
     <row r="151">
@@ -2279,11 +2279,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>RRAS18</t>
+          <t>RRAS 17</t>
         </is>
       </c>
       <c r="C151">
-        <v>62</v>
+        <v>226</v>
       </c>
     </row>
     <row r="152">
@@ -2292,123 +2292,123 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>RRAS19</t>
+          <t>RRAS 18</t>
         </is>
       </c>
       <c r="C152">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="153">
       <c r="A153">
         <v>2019</v>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>RRAS2</t>
-        </is>
-      </c>
       <c r="C153">
-        <v>360</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>RRAS3</t>
+          <t>RRAS 1</t>
         </is>
       </c>
       <c r="C154">
-        <v>76</v>
+        <v>192</v>
       </c>
     </row>
     <row r="155">
       <c r="A155">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>RRAS4</t>
+          <t>RRAS 2</t>
         </is>
       </c>
       <c r="C155">
-        <v>147</v>
+        <v>389</v>
       </c>
     </row>
     <row r="156">
       <c r="A156">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>RRAS5</t>
+          <t>RRAS 3</t>
         </is>
       </c>
       <c r="C156">
-        <v>239</v>
+        <v>89</v>
       </c>
     </row>
     <row r="157">
       <c r="A157">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>RRAS6</t>
+          <t>RRAS 4</t>
         </is>
       </c>
       <c r="C157">
-        <v>1185</v>
+        <v>149</v>
       </c>
     </row>
     <row r="158">
       <c r="A158">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>RRAS7</t>
+          <t>RRAS 5</t>
         </is>
       </c>
       <c r="C158">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="159">
       <c r="A159">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>RRAS8</t>
+          <t>RRAS 6</t>
         </is>
       </c>
       <c r="C159">
-        <v>219</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="160">
       <c r="A160">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>RRAS9</t>
+          <t>RRAS 7</t>
         </is>
       </c>
       <c r="C160">
-        <v>139</v>
+        <v>229</v>
       </c>
     </row>
     <row r="161">
       <c r="A161">
-        <v>2019</v>
+        <v>2020</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>RRAS 8</t>
+        </is>
       </c>
       <c r="C161">
-        <v>1</v>
+        <v>238</v>
       </c>
     </row>
     <row r="162">
@@ -2417,11 +2417,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>RRAS1</t>
+          <t>RRAS 9</t>
         </is>
       </c>
       <c r="C162">
-        <v>192</v>
+        <v>162</v>
       </c>
     </row>
     <row r="163">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>RRAS10</t>
+          <t>RRAS 10</t>
         </is>
       </c>
       <c r="C163">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>RRAS11</t>
+          <t>RRAS 11</t>
         </is>
       </c>
       <c r="C164">
@@ -2456,11 +2456,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>RRAS12</t>
+          <t>RRAS 12</t>
         </is>
       </c>
       <c r="C165">
-        <v>93</v>
+        <v>148</v>
       </c>
     </row>
     <row r="166">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>RRAS13</t>
+          <t>RRAS 13</t>
         </is>
       </c>
       <c r="C166">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>RRAS14</t>
+          <t>RRAS 14</t>
         </is>
       </c>
       <c r="C167">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>RRAS15</t>
+          <t>RRAS 15</t>
         </is>
       </c>
       <c r="C168">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>RRAS16</t>
+          <t>RRAS 16</t>
         </is>
       </c>
       <c r="C169">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>RRAS17</t>
+          <t>RRAS 17</t>
         </is>
       </c>
       <c r="C170">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>RRAS18</t>
+          <t>RRAS 18</t>
         </is>
       </c>
       <c r="C171">
@@ -2545,125 +2545,125 @@
       <c r="A172">
         <v>2020</v>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>RRAS19</t>
-        </is>
-      </c>
       <c r="C172">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>RRAS2</t>
+          <t>RRAS 1</t>
         </is>
       </c>
       <c r="C173">
-        <v>389</v>
+        <v>216</v>
       </c>
     </row>
     <row r="174">
       <c r="A174">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>RRAS3</t>
+          <t>RRAS 2</t>
         </is>
       </c>
       <c r="C174">
-        <v>89</v>
+        <v>357</v>
       </c>
     </row>
     <row r="175">
       <c r="A175">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>RRAS4</t>
+          <t>RRAS 3</t>
         </is>
       </c>
       <c r="C175">
-        <v>149</v>
+        <v>76</v>
       </c>
     </row>
     <row r="176">
       <c r="A176">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>RRAS5</t>
+          <t>RRAS 4</t>
         </is>
       </c>
       <c r="C176">
-        <v>232</v>
+        <v>151</v>
       </c>
     </row>
     <row r="177">
       <c r="A177">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>RRAS6</t>
+          <t>RRAS 5</t>
         </is>
       </c>
       <c r="C177">
-        <v>1106</v>
+        <v>202</v>
       </c>
     </row>
     <row r="178">
       <c r="A178">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>RRAS7</t>
+          <t>RRAS 6</t>
         </is>
       </c>
       <c r="C178">
-        <v>229</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="179">
       <c r="A179">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>RRAS8</t>
+          <t>RRAS 7</t>
         </is>
       </c>
       <c r="C179">
-        <v>238</v>
+        <v>227</v>
       </c>
     </row>
     <row r="180">
       <c r="A180">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>RRAS9</t>
+          <t>RRAS 8</t>
         </is>
       </c>
       <c r="C180">
-        <v>162</v>
+        <v>241</v>
       </c>
     </row>
     <row r="181">
       <c r="A181">
-        <v>2020</v>
+        <v>2021</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>RRAS 9</t>
+        </is>
       </c>
       <c r="C181">
-        <v>1</v>
+        <v>169</v>
       </c>
     </row>
     <row r="182">
@@ -2672,11 +2672,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>RRAS1</t>
+          <t>RRAS 10</t>
         </is>
       </c>
       <c r="C182">
-        <v>216</v>
+        <v>88</v>
       </c>
     </row>
     <row r="183">
@@ -2685,11 +2685,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>RRAS10</t>
+          <t>RRAS 11</t>
         </is>
       </c>
       <c r="C183">
-        <v>88</v>
+        <v>59</v>
       </c>
     </row>
     <row r="184">
@@ -2698,11 +2698,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>RRAS11</t>
+          <t>RRAS 12</t>
         </is>
       </c>
       <c r="C184">
-        <v>59</v>
+        <v>170</v>
       </c>
     </row>
     <row r="185">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>RRAS12</t>
+          <t>RRAS 13</t>
         </is>
       </c>
       <c r="C185">
-        <v>116</v>
+        <v>231</v>
       </c>
     </row>
     <row r="186">
@@ -2724,11 +2724,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>RRAS13</t>
+          <t>RRAS 14</t>
         </is>
       </c>
       <c r="C186">
-        <v>231</v>
+        <v>134</v>
       </c>
     </row>
     <row r="187">
@@ -2737,11 +2737,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RRAS14</t>
+          <t>RRAS 15</t>
         </is>
       </c>
       <c r="C187">
-        <v>134</v>
+        <v>316</v>
       </c>
     </row>
     <row r="188">
@@ -2750,11 +2750,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RRAS15</t>
+          <t>RRAS 16</t>
         </is>
       </c>
       <c r="C188">
-        <v>316</v>
+        <v>125</v>
       </c>
     </row>
     <row r="189">
@@ -2763,11 +2763,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>RRAS16</t>
+          <t>RRAS 17</t>
         </is>
       </c>
       <c r="C189">
-        <v>125</v>
+        <v>215</v>
       </c>
     </row>
     <row r="190">
@@ -2776,59 +2776,54 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>RRAS17</t>
+          <t>RRAS 18</t>
         </is>
       </c>
       <c r="C190">
-        <v>215</v>
+        <v>90</v>
       </c>
     </row>
     <row r="191">
       <c r="A191">
         <v>2021</v>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>RRAS18</t>
-        </is>
-      </c>
       <c r="C191">
-        <v>90</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192">
       <c r="A192">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>RRAS19</t>
+          <t>RRAS 1</t>
         </is>
       </c>
       <c r="C192">
-        <v>54</v>
+        <v>207</v>
       </c>
     </row>
     <row r="193">
       <c r="A193">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>RRAS2</t>
+          <t>RRAS 2</t>
         </is>
       </c>
       <c r="C193">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="194">
       <c r="A194">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>RRAS3</t>
+          <t>RRAS 3</t>
         </is>
       </c>
       <c r="C194">
@@ -2837,88 +2832,93 @@
     </row>
     <row r="195">
       <c r="A195">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>RRAS4</t>
+          <t>RRAS 4</t>
         </is>
       </c>
       <c r="C195">
-        <v>151</v>
+        <v>122</v>
       </c>
     </row>
     <row r="196">
       <c r="A196">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>RRAS5</t>
+          <t>RRAS 5</t>
         </is>
       </c>
       <c r="C196">
-        <v>202</v>
+        <v>222</v>
       </c>
     </row>
     <row r="197">
       <c r="A197">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>RRAS6</t>
+          <t>RRAS 6</t>
         </is>
       </c>
       <c r="C197">
-        <v>1054</v>
+        <v>962</v>
       </c>
     </row>
     <row r="198">
       <c r="A198">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>RRAS7</t>
+          <t>RRAS 7</t>
         </is>
       </c>
       <c r="C198">
-        <v>227</v>
+        <v>199</v>
       </c>
     </row>
     <row r="199">
       <c r="A199">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>RRAS8</t>
+          <t>RRAS 8</t>
         </is>
       </c>
       <c r="C199">
-        <v>241</v>
+        <v>223</v>
       </c>
     </row>
     <row r="200">
       <c r="A200">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>RRAS9</t>
+          <t>RRAS 9</t>
         </is>
       </c>
       <c r="C200">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="201">
       <c r="A201">
-        <v>2021</v>
+        <v>2022</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>RRAS 10</t>
+        </is>
       </c>
       <c r="C201">
-        <v>3</v>
+        <v>88</v>
       </c>
     </row>
     <row r="202">
@@ -2927,11 +2927,11 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>RRAS1</t>
+          <t>RRAS 11</t>
         </is>
       </c>
       <c r="C202">
-        <v>207</v>
+        <v>56</v>
       </c>
     </row>
     <row r="203">
@@ -2940,11 +2940,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>RRAS10</t>
+          <t>RRAS 12</t>
         </is>
       </c>
       <c r="C203">
-        <v>88</v>
+        <v>181</v>
       </c>
     </row>
     <row r="204">
@@ -2953,11 +2953,11 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>RRAS11</t>
+          <t>RRAS 13</t>
         </is>
       </c>
       <c r="C204">
-        <v>56</v>
+        <v>249</v>
       </c>
     </row>
     <row r="205">
@@ -2966,11 +2966,11 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>RRAS12</t>
+          <t>RRAS 14</t>
         </is>
       </c>
       <c r="C205">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="206">
@@ -2979,11 +2979,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>RRAS13</t>
+          <t>RRAS 15</t>
         </is>
       </c>
       <c r="C206">
-        <v>249</v>
+        <v>302</v>
       </c>
     </row>
     <row r="207">
@@ -2992,11 +2992,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>RRAS14</t>
+          <t>RRAS 16</t>
         </is>
       </c>
       <c r="C207">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="208">
@@ -3005,11 +3005,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>RRAS15</t>
+          <t>RRAS 17</t>
         </is>
       </c>
       <c r="C208">
-        <v>302</v>
+        <v>236</v>
       </c>
     </row>
     <row r="209">
@@ -3018,162 +3018,162 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>RRAS16</t>
+          <t>RRAS 18</t>
         </is>
       </c>
       <c r="C209">
-        <v>124</v>
+        <v>89</v>
       </c>
     </row>
     <row r="210">
       <c r="A210">
         <v>2022</v>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>RRAS17</t>
-        </is>
-      </c>
       <c r="C210">
-        <v>236</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>RRAS18</t>
+          <t>RRAS 1</t>
         </is>
       </c>
       <c r="C211">
-        <v>89</v>
+        <v>190</v>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>RRAS19</t>
+          <t>RRAS 2</t>
         </is>
       </c>
       <c r="C212">
-        <v>62</v>
+        <v>387</v>
       </c>
     </row>
     <row r="213">
       <c r="A213">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>RRAS2</t>
+          <t>RRAS 3</t>
         </is>
       </c>
       <c r="C213">
-        <v>351</v>
+        <v>68</v>
       </c>
     </row>
     <row r="214">
       <c r="A214">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>RRAS3</t>
+          <t>RRAS 4</t>
         </is>
       </c>
       <c r="C214">
-        <v>76</v>
+        <v>140</v>
       </c>
     </row>
     <row r="215">
       <c r="A215">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>RRAS4</t>
+          <t>RRAS 5</t>
         </is>
       </c>
       <c r="C215">
-        <v>122</v>
+        <v>191</v>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>RRAS5</t>
+          <t>RRAS 6</t>
         </is>
       </c>
       <c r="C216">
-        <v>222</v>
+        <v>954</v>
       </c>
     </row>
     <row r="217">
       <c r="A217">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>RRAS6</t>
+          <t>RRAS 7</t>
         </is>
       </c>
       <c r="C217">
-        <v>962</v>
+        <v>208</v>
       </c>
     </row>
     <row r="218">
       <c r="A218">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>RRAS7</t>
+          <t>RRAS 8</t>
         </is>
       </c>
       <c r="C218">
-        <v>199</v>
+        <v>232</v>
       </c>
     </row>
     <row r="219">
       <c r="A219">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>RRAS8</t>
+          <t>RRAS 9</t>
         </is>
       </c>
       <c r="C219">
-        <v>223</v>
+        <v>155</v>
       </c>
     </row>
     <row r="220">
       <c r="A220">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>RRAS9</t>
+          <t>RRAS 10</t>
         </is>
       </c>
       <c r="C220">
-        <v>166</v>
+        <v>92</v>
       </c>
     </row>
     <row r="221">
       <c r="A221">
-        <v>2022</v>
+        <v>2023</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>RRAS 11</t>
+        </is>
       </c>
       <c r="C221">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="222">
@@ -3182,11 +3182,11 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>RRAS1</t>
+          <t>RRAS 12</t>
         </is>
       </c>
       <c r="C222">
-        <v>190</v>
+        <v>151</v>
       </c>
     </row>
     <row r="223">
@@ -3195,11 +3195,11 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>RRAS10</t>
+          <t>RRAS 13</t>
         </is>
       </c>
       <c r="C223">
-        <v>92</v>
+        <v>229</v>
       </c>
     </row>
     <row r="224">
@@ -3208,11 +3208,11 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>RRAS11</t>
+          <t>RRAS 14</t>
         </is>
       </c>
       <c r="C224">
-        <v>45</v>
+        <v>126</v>
       </c>
     </row>
     <row r="225">
@@ -3221,11 +3221,11 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>RRAS12</t>
+          <t>RRAS 15</t>
         </is>
       </c>
       <c r="C225">
-        <v>93</v>
+        <v>306</v>
       </c>
     </row>
     <row r="226">
@@ -3234,11 +3234,11 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>RRAS13</t>
+          <t>RRAS 16</t>
         </is>
       </c>
       <c r="C226">
-        <v>229</v>
+        <v>115</v>
       </c>
     </row>
     <row r="227">
@@ -3247,11 +3247,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>RRAS14</t>
+          <t>RRAS 17</t>
         </is>
       </c>
       <c r="C227">
-        <v>126</v>
+        <v>209</v>
       </c>
     </row>
     <row r="228">
@@ -3260,175 +3260,261 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>RRAS15</t>
+          <t>RRAS 18</t>
         </is>
       </c>
       <c r="C228">
-        <v>306</v>
+        <v>84</v>
       </c>
     </row>
     <row r="229">
       <c r="A229">
         <v>2023</v>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>RRAS16</t>
-        </is>
-      </c>
       <c r="C229">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="230">
       <c r="A230">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>RRAS17</t>
+          <t>RRAS 1</t>
         </is>
       </c>
       <c r="C230">
-        <v>209</v>
+        <v>154</v>
       </c>
     </row>
     <row r="231">
       <c r="A231">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>RRAS18</t>
+          <t>RRAS 2</t>
         </is>
       </c>
       <c r="C231">
-        <v>84</v>
+        <v>319</v>
       </c>
     </row>
     <row r="232">
       <c r="A232">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>RRAS19</t>
+          <t>RRAS 3</t>
         </is>
       </c>
       <c r="C232">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>RRAS2</t>
+          <t>RRAS 4</t>
         </is>
       </c>
       <c r="C233">
-        <v>387</v>
+        <v>117</v>
       </c>
     </row>
     <row r="234">
       <c r="A234">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>RRAS3</t>
+          <t>RRAS 5</t>
         </is>
       </c>
       <c r="C234">
-        <v>68</v>
+        <v>176</v>
       </c>
     </row>
     <row r="235">
       <c r="A235">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>RRAS4</t>
+          <t>RRAS 6</t>
         </is>
       </c>
       <c r="C235">
-        <v>140</v>
+        <v>861</v>
       </c>
     </row>
     <row r="236">
       <c r="A236">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>RRAS5</t>
+          <t>RRAS 7</t>
         </is>
       </c>
       <c r="C236">
-        <v>191</v>
+        <v>148</v>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>RRAS6</t>
+          <t>RRAS 8</t>
         </is>
       </c>
       <c r="C237">
-        <v>954</v>
+        <v>206</v>
       </c>
     </row>
     <row r="238">
       <c r="A238">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>RRAS7</t>
+          <t>RRAS 9</t>
         </is>
       </c>
       <c r="C238">
-        <v>208</v>
+        <v>135</v>
       </c>
     </row>
     <row r="239">
       <c r="A239">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>RRAS8</t>
+          <t>RRAS 10</t>
         </is>
       </c>
       <c r="C239">
-        <v>232</v>
+        <v>65</v>
       </c>
     </row>
     <row r="240">
       <c r="A240">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>RRAS9</t>
+          <t>RRAS 11</t>
         </is>
       </c>
       <c r="C240">
-        <v>155</v>
+        <v>56</v>
       </c>
     </row>
     <row r="241">
       <c r="A241">
-        <v>2023</v>
+        <v>2024</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>RRAS 12</t>
+        </is>
       </c>
       <c r="C241">
-        <v>6</v>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>2024</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>RRAS 13</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>2024</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>RRAS 14</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>2024</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>RRAS 15</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>2024</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>RRAS 16</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>2024</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>RRAS 17</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>2024</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>RRAS 18</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>2024</v>
+      </c>
+      <c r="C248">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
